--- a/output/pdf_financials_xlsx/VTI.xlsx
+++ b/output/pdf_financials_xlsx/VTI.xlsx
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.049464</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.069951</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.08870500000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.049464</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.069951</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.08870500000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.055135</v>
+        <v>0.005671</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.106524</v>
+        <v>0.036573</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.130657</v>
+        <v>0.041952</v>
       </c>
     </row>
     <row r="49">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/VTI.xlsx
+++ b/output/pdf_financials_xlsx/VTI.xlsx
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.008026</v>
       </c>
     </row>
     <row r="101">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.008026</v>
+        <v>0.008026</v>
       </c>
     </row>
     <row r="88">
